--- a/Dummy tables/In-process - dummy tables.xlsx
+++ b/Dummy tables/In-process - dummy tables.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tropichealthcom.sharepoint.com/sites/Projects77/Projects  Open/C033 - OPITACA/60 - Implementation/WS3 - Data and cLQAS/TH adaptable tools/Analysis scripts/clqas-tools/Dummy tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tropichealthcom.sharepoint.com/sites/Projects77/Projects  Open/C033 - OPITACA/60 - Implementation/WS3 - Data and cLQAS/TH adaptable tools/AMP toolkit/amp-clqas-toolkit/Dummy tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3029" documentId="6_{4C8E3B7F-99FB-4B5D-A4B6-7762B8337465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FD4EA38-43CA-4974-B107-549DC96F6EEF}"/>
+  <xr:revisionPtr revIDLastSave="3066" documentId="6_{4C8E3B7F-99FB-4B5D-A4B6-7762B8337465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84ADA112-01C6-478E-BBC3-0A79B7E40BD7}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="30705" yWindow="1500" windowWidth="19185" windowHeight="10065" tabRatio="869" firstSheet="3" activeTab="10" xr2:uid="{C6888998-64C4-4FB1-A8CF-30DA95DD3E6B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="869" firstSheet="7" activeTab="10" xr2:uid="{C6888998-64C4-4FB1-A8CF-30DA95DD3E6B}"/>
   </bookViews>
   <sheets>
-    <sheet name="A1 Completeness" sheetId="4" r:id="rId1"/>
-    <sheet name="A2 Error line list" sheetId="5" r:id="rId2"/>
-    <sheet name="A3 Trend in total errors" sheetId="6" r:id="rId3"/>
-    <sheet name="A4 Errors by district" sheetId="7" r:id="rId4"/>
-    <sheet name="A5 Errors by region" sheetId="8" r:id="rId5"/>
-    <sheet name="A6. Map of errors by district" sheetId="11" r:id="rId6"/>
-    <sheet name="A7. Error reasons by district" sheetId="9" r:id="rId7"/>
-    <sheet name="A8. Error reasons by region" sheetId="10" r:id="rId8"/>
-    <sheet name="A9. Errors - campaign summary" sheetId="12" r:id="rId9"/>
-    <sheet name="A10. Error reasons - summary" sheetId="13" r:id="rId10"/>
+    <sheet name="Table 1 Completeness" sheetId="4" r:id="rId1"/>
+    <sheet name="Table 2 Error line list" sheetId="5" r:id="rId2"/>
+    <sheet name="Table 3 Trend in total errors" sheetId="6" r:id="rId3"/>
+    <sheet name="Table 4 Errors by district" sheetId="7" r:id="rId4"/>
+    <sheet name="Table 5 Errors by region" sheetId="8" r:id="rId5"/>
+    <sheet name="Map of errors by district" sheetId="11" r:id="rId6"/>
+    <sheet name="Tab7 Error reasons by district" sheetId="9" r:id="rId7"/>
+    <sheet name="Table 8 Error reasons by region" sheetId="10" r:id="rId8"/>
+    <sheet name="Tab9 Errors - campaign summary" sheetId="12" r:id="rId9"/>
+    <sheet name="Tab 10 Error reasons - summary" sheetId="13" r:id="rId10"/>
     <sheet name="Lot classification" sheetId="14" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -93,23 +93,6 @@
   <si>
     <t>Lot complete
 (Y/N)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Table A2. Daily error and error reason line list
-Assessment day: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="7"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1</t>
-    </r>
   </si>
   <si>
     <t>Reason
@@ -222,50 +205,7 @@
     </r>
   </si>
   <si>
-    <t>Table A3. Percentage of households with HHR errors, by assessment day</t>
-  </si>
-  <si>
     <t>Total</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Table A4. Percentage of households with HHR errors by district for a given region, daily and cumulative total
-Region: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="7"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Region 1</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Assessment day: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="7"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Day 2</t>
-    </r>
   </si>
   <si>
     <t>Assessment day results</t>
@@ -274,36 +214,10 @@
     <t>Cumulative results</t>
   </si>
   <si>
-    <t xml:space="preserve">Table A4. Percentage of households with HHR errors by district for a given region, daily and cumulative total
-Region: 
-Assessment day: </t>
-  </si>
-  <si>
     <t>Number of HHs</t>
   </si>
   <si>
     <t>Percentage of HH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table A5. Percentage of households with HHR errors by region, daily and cumulative total
-Assessment day: </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Table A5. Percentage of households with HHR errors by region, daily and cumulative total
-Assessment day: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="7"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Day 2</t>
-    </r>
   </si>
   <si>
     <t>Region 3</t>
@@ -492,12 +406,6 @@
   </si>
   <si>
     <t>Total households assessed</t>
-  </si>
-  <si>
-    <t>Table A9. Campaign assessment summary of total HHR errors and direction of error</t>
-  </si>
-  <si>
-    <t>Table A10. Campaign summary of assessment outcomes and categorised reasons for errors</t>
   </si>
   <si>
     <t>Household likely inflated number of eligible persons</t>
@@ -792,18 +700,90 @@
     <t>Example of completed table (cumulative)</t>
   </si>
   <si>
-    <t>Classification of lots based on correct count of eligible persons during HHR.
-Region 1. May 2025.</t>
-  </si>
-  <si>
     <t>Name of district (lot)</t>
   </si>
   <si>
     <t>Output A6 is one or more map(s) of the count of HHR errors for a given assessment day</t>
   </si>
   <si>
+    <t>HHR counted ineligible person as eligible</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Table A7a. Distribution of HHR error reasons by district for a given region, daily
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Decision rules for classification
+(assuming 60 HH denominator):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+0-3 failures = Good
+4-8 failures = Uncertain
+9+ failures = Inadequate</t>
+    </r>
+  </si>
+  <si>
+    <t>Table 1. Completeness and HHR errors by district
+Assessment day:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Table 1. Completeness and HHR errors by district
+Assessment day: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Table 2. Daily error and error reason line list
+Assessment day: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>Table 3. Percentage of households with HHR errors, by assessment day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 4. Percentage of households with HHR errors by district for a given region, daily and cumulative total
+Region: 
+Assessment day: </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Table 4. Percentage of households with HHR errors by district for a given region, daily and cumulative total
 Region: </t>
     </r>
     <r>
@@ -842,18 +822,39 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Table A7a. Distribution of HHR error reasons by district for a given region, daily
+    <t xml:space="preserve">Table 5. Percentage of households with HHR errors by region, daily and cumulative total
+Assessment day: </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Table 5. Percentage of households with HHR errors by region, daily and cumulative total
+Assessment day: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Day 2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 7a. Distribution of HHR error reasons by district for a given region, daily
 Region: 
 Assessment day: </t>
   </si>
   <si>
-    <t xml:space="preserve">Table A7b. Distribution of HHR error reasons by district for a given region, cumulative
+    <t xml:space="preserve">Table 7b. Distribution of HHR error reasons by district for a given region, cumulative
 Region: 
 Assessment day: </t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Table A7b. Distribution of HHR error reasons by district for a given region, cumulative
+      <t xml:space="preserve">Table 7b. Distribution of HHR error reasons by district for a given region, cumulative
 Region: </t>
     </r>
     <r>
@@ -892,12 +893,31 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Table A8a. Distribution of HHR error reasons by region, daily
-Assessment day: </t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">Table A8a. Distribution of HHR error reasons by region, daily
+      <t xml:space="preserve">Table 7a. Distribution of HHR error reasons by district for a given region, daily
+Region: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Region 1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 Assessment day: </t>
     </r>
     <r>
@@ -913,12 +933,12 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Table A8b. Distribution of HHR error reasons by region, cumulative
+    <t xml:space="preserve">Table 8a. Distribution of HHR error reasons by region, daily
 Assessment day: </t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Table A8b. Distribution of HHR error reasons by region, cumulative
+      <t xml:space="preserve">Table 8a. Distribution of HHR error reasons by region, daily
 Assessment day: </t>
     </r>
     <r>
@@ -935,7 +955,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Table A1. Completeness and HHR errors by district
+      <t xml:space="preserve">Table 8b. Distribution of HHR error reasons by region, cumulative
 Assessment day: </t>
     </r>
     <r>
@@ -947,42 +967,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>1</t>
+      <t>Day 2</t>
     </r>
   </si>
   <si>
-    <t>Table A1. Completeness and HHR errors by district
-Assessment day:</t>
+    <t xml:space="preserve">Table 8b. Distribution of HHR error reasons by region, cumulative
+Assessment day: </t>
   </si>
   <si>
-    <t>HHR counted ineligible person as eligible</t>
+    <t>Table 9. Campaign assessment summary of total HHR errors and direction of error</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Decision rules for classification
-(assuming 60 HH denominator):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-0-3 failures = Good
-4-8 failures = Uncertain
-9+ failures = Inadequate</t>
-    </r>
+    <t>Table 10. Campaign summary of assessment outcomes and categorised reasons for errors</t>
+  </si>
+  <si>
+    <t>Classification of lots based on correct count of eligible persons during HHR.
+Region 1.</t>
   </si>
 </sst>
 </file>
@@ -1715,24 +1715,30 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1745,6 +1751,24 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1763,24 +1787,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -1793,29 +1799,23 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1898,7 +1898,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-GB" sz="1100" b="1"/>
-              <a:t>A3. Percentage</a:t>
+              <a:t>3. Percentage</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-GB" sz="1100" b="1" baseline="0"/>
@@ -1962,7 +1962,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'A3 Trend in total errors'!$D$18</c:f>
+              <c:f>'Table 3 Trend in total errors'!$D$18</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2026,7 +2026,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'A3 Trend in total errors'!$B$19:$B$24</c:f>
+              <c:f>'Table 3 Trend in total errors'!$B$19:$B$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2053,7 +2053,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'A3 Trend in total errors'!$D$19:$D$24</c:f>
+              <c:f>'Table 3 Trend in total errors'!$D$19:$D$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2105,7 +2105,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'A3 Trend in total errors'!$E$18</c:f>
+              <c:f>'Table 3 Trend in total errors'!$E$18</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2128,7 +2128,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'A3 Trend in total errors'!$B$19:$B$24</c:f>
+              <c:f>'Table 3 Trend in total errors'!$B$19:$B$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2155,7 +2155,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'A3 Trend in total errors'!$E$19:$E$24</c:f>
+              <c:f>'Table 3 Trend in total errors'!$E$19:$E$24</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2658,7 +2658,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-GB" sz="1100" b="1"/>
-              <a:t>A3. Percentage</a:t>
+              <a:t>3. Percentage</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-GB" sz="1100" b="1" baseline="0"/>
@@ -2722,7 +2722,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'A3 Trend in total errors'!$D$5</c:f>
+              <c:f>'Table 3 Trend in total errors'!$D$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2743,7 +2743,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'A3 Trend in total errors'!$B$6:$B$11</c:f>
+              <c:f>'Table 3 Trend in total errors'!$B$6:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2770,7 +2770,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'A3 Trend in total errors'!$D$6:$D$11</c:f>
+              <c:f>'Table 3 Trend in total errors'!$D$6:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2804,7 +2804,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'A3 Trend in total errors'!$E$5</c:f>
+              <c:f>'Table 3 Trend in total errors'!$E$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2827,7 +2827,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'A3 Trend in total errors'!$B$19:$B$24</c:f>
+              <c:f>'Table 3 Trend in total errors'!$B$19:$B$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2854,7 +2854,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'A3 Trend in total errors'!$E$6:$E$11</c:f>
+              <c:f>'Table 3 Trend in total errors'!$E$6:$E$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -4802,22 +4802,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B2" s="97" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
+      <c r="B2" s="98" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
     </row>
     <row r="4" spans="2:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="99" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
+      <c r="B4" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
     </row>
     <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
@@ -4914,31 +4914,31 @@
       <c r="F16" s="10"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B17" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="96"/>
-      <c r="D17" s="96"/>
-      <c r="E17" s="96"/>
-      <c r="F17" s="96"/>
+      <c r="B17" s="100" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="100"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="100"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B20" s="97" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="98"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
+      <c r="B20" s="98" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
     </row>
     <row r="22" spans="2:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="99" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="99"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="99"/>
+      <c r="B22" s="101" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="101"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="101"/>
     </row>
     <row r="23" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B35" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="96"/>
+      <c r="B35" s="100" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="100"/>
+      <c r="D35" s="100"/>
+      <c r="E35" s="100"/>
+      <c r="F35" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -5182,64 +5182,64 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B2" s="97" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="H2" s="97" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
+      <c r="B2" s="98" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="H2" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="99" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="H4" s="99" t="s">
-        <v>76</v>
-      </c>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
+      <c r="B4" s="101" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="H4" s="101" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
     </row>
     <row r="5" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
       <c r="C5" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="J5" s="77" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="K5" s="77" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="29" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C6" s="59"/>
       <c r="D6" s="63"/>
       <c r="E6" s="65"/>
       <c r="H6" s="29" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="I6" s="62">
         <v>2400</v>
@@ -5249,13 +5249,13 @@
     </row>
     <row r="7" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="57" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="9"/>
       <c r="E7" s="68"/>
       <c r="H7" s="57" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I7" s="23">
         <v>1562</v>
@@ -5268,13 +5268,13 @@
     </row>
     <row r="8" spans="2:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="74" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C8" s="83"/>
       <c r="D8" s="84"/>
       <c r="E8" s="69"/>
       <c r="H8" s="74" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I8" s="75">
         <v>838</v>
@@ -5287,13 +5287,13 @@
     </row>
     <row r="9" spans="2:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="70" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C9" s="85"/>
       <c r="D9" s="86"/>
       <c r="E9" s="87"/>
       <c r="H9" s="70" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I9" s="71">
         <v>720</v>
@@ -5309,13 +5309,13 @@
     </row>
     <row r="10" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="58" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="9"/>
       <c r="E10" s="27"/>
       <c r="H10" s="58" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="I10" s="23">
         <v>305</v>
@@ -5331,13 +5331,13 @@
     </row>
     <row r="11" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="58" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="9"/>
       <c r="E11" s="27"/>
       <c r="H11" s="58" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I11" s="23">
         <v>88</v>
@@ -5353,13 +5353,13 @@
     </row>
     <row r="12" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="58" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="9"/>
       <c r="E12" s="27"/>
       <c r="H12" s="58" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I12" s="23">
         <v>262</v>
@@ -5375,13 +5375,13 @@
     </row>
     <row r="13" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="58" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="9"/>
       <c r="E13" s="27"/>
       <c r="H13" s="58" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I13" s="23">
         <v>46</v>
@@ -5397,13 +5397,13 @@
     </row>
     <row r="14" spans="2:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="58" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="9"/>
       <c r="E14" s="27"/>
       <c r="H14" s="58" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I14" s="23">
         <v>19</v>
@@ -5419,13 +5419,13 @@
     </row>
     <row r="15" spans="2:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="70" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C15" s="85"/>
       <c r="D15" s="86"/>
       <c r="E15" s="87"/>
       <c r="H15" s="70" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I15" s="71">
         <v>118</v>
@@ -5441,13 +5441,13 @@
     </row>
     <row r="16" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="58" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="19"/>
       <c r="E16" s="60"/>
       <c r="H16" s="58" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I16" s="23">
         <v>80</v>
@@ -5463,13 +5463,13 @@
     </row>
     <row r="17" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="58" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="9"/>
       <c r="E17" s="27"/>
       <c r="H17" s="58" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I17" s="23">
         <v>22</v>
@@ -5485,13 +5485,13 @@
     </row>
     <row r="18" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="58" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="9"/>
       <c r="E18" s="27"/>
       <c r="H18" s="58" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I18" s="23">
         <v>16</v>
@@ -5506,18 +5506,18 @@
       </c>
     </row>
     <row r="19" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="96" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="96"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
-      <c r="H19" s="96" t="s">
-        <v>93</v>
-      </c>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="96"/>
+      <c r="B19" s="100" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="100"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="H19" s="100" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="100"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="100"/>
     </row>
     <row r="20" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
@@ -5550,47 +5550,47 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B2" s="97" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="F2" s="97" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
+      <c r="B2" s="98" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="F2" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
     </row>
     <row r="4" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="128" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="F4" s="128" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
+      <c r="B4" s="96" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="F4" s="96" t="s">
+        <v>119</v>
+      </c>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
     </row>
     <row r="5" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5690,14 +5690,14 @@
     </row>
     <row r="11" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="5">
         <v>8</v>
       </c>
       <c r="D11" s="93"/>
       <c r="F11" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" s="5">
         <v>8</v>
@@ -5709,14 +5709,14 @@
     </row>
     <row r="12" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5">
         <v>0</v>
       </c>
       <c r="D12" s="93"/>
       <c r="F12" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12" s="5">
         <v>0</v>
@@ -5728,14 +5728,14 @@
     </row>
     <row r="13" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="5">
         <v>12</v>
       </c>
       <c r="D13" s="93"/>
       <c r="F13" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" s="5">
         <v>12</v>
@@ -5747,14 +5747,14 @@
     </row>
     <row r="14" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="5">
         <v>9</v>
       </c>
       <c r="D14" s="93"/>
       <c r="F14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G14" s="5">
         <v>9</v>
@@ -5766,14 +5766,14 @@
     </row>
     <row r="15" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="5">
         <v>4</v>
       </c>
       <c r="D15" s="93"/>
       <c r="F15" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G15" s="5">
         <v>4</v>
@@ -5784,28 +5784,28 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="129" t="s">
+      <c r="B16" s="97" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="97"/>
+      <c r="D16" s="97"/>
+      <c r="F16" s="97" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="97"/>
+      <c r="H16" s="97"/>
+    </row>
+    <row r="17" spans="2:8" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="97" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="F16" s="129" t="s">
+      <c r="C17" s="97"/>
+      <c r="D17" s="97"/>
+      <c r="F17" s="97" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
-    </row>
-    <row r="17" spans="2:8" ht="75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="129" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="129"/>
-      <c r="D17" s="129"/>
-      <c r="F17" s="129" t="s">
-        <v>119</v>
-      </c>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
+      <c r="G17" s="97"/>
+      <c r="H17" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5850,57 +5850,57 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B2" s="97" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
+      <c r="B2" s="98" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
     </row>
     <row r="4" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="99" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
+      <c r="B4" s="101" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="D5" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E5" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="F5" s="18" t="s">
         <v>30</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>31</v>
       </c>
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
     </row>
     <row r="6" spans="2:8" ht="26" x14ac:dyDescent="0.35">
       <c r="B6" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="18" t="s">
         <v>33</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>34</v>
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
@@ -5910,22 +5910,22 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6001,68 +6001,68 @@
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
+      <c r="B16" s="100" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="100"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B19" s="97" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="97"/>
-      <c r="H19" s="97"/>
+      <c r="B19" s="98" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="98"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="98"/>
     </row>
     <row r="21" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="99" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="99"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="99"/>
-      <c r="H21" s="99"/>
+      <c r="B21" s="101" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="101"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="101"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B22" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="D22" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="E22" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="F22" s="18" t="s">
         <v>30</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>31</v>
       </c>
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
     </row>
     <row r="23" spans="2:8" ht="26" x14ac:dyDescent="0.35">
       <c r="B23" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
       <c r="E23" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="18" t="s">
         <v>33</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>34</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
@@ -6072,22 +6072,22 @@
         <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6107,10 +6107,10 @@
         <v>2</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6130,10 +6130,10 @@
         <v>2</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6153,10 +6153,10 @@
         <v>8</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6176,10 +6176,10 @@
         <v>4</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6229,15 +6229,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B33" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="96"/>
-      <c r="G33" s="96"/>
-      <c r="H33" s="96"/>
+      <c r="B33" s="100" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="100"/>
+      <c r="D33" s="100"/>
+      <c r="E33" s="100"/>
+      <c r="F33" s="100"/>
+      <c r="G33" s="100"/>
+      <c r="H33" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -6266,33 +6266,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B2" s="97" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
+      <c r="B2" s="98" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
     </row>
     <row r="4" spans="2:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="99" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
+      <c r="B4" s="101" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
     </row>
     <row r="5" spans="2:5" ht="29" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6344,53 +6344,53 @@
       <c r="E11" s="9"/>
     </row>
     <row r="12" spans="2:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="96" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
+      <c r="B12" s="100" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="100"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="100"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B13" s="101"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="100"/>
+      <c r="B13" s="102"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B14" s="101"/>
-      <c r="C14" s="100"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="100"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B15" s="97" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="98"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
+      <c r="B15" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
     </row>
     <row r="17" spans="2:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="99" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="99"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="99"/>
+      <c r="B17" s="101" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="101"/>
+      <c r="D17" s="101"/>
+      <c r="E17" s="101"/>
     </row>
     <row r="18" spans="2:5" ht="29" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6484,37 +6484,37 @@
       </c>
     </row>
     <row r="25" spans="2:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="96" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="96"/>
-      <c r="D25" s="96"/>
-      <c r="E25" s="96"/>
+      <c r="B25" s="100" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="100"/>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B26" s="100"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="100"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="103"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B27" s="100"/>
-      <c r="C27" s="100"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="100"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B25:E25"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B25:E25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -6538,56 +6538,56 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B2" s="97" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="98" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
     </row>
     <row r="4" spans="2:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="99" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
+      <c r="B4" s="101" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="13"/>
-      <c r="C5" s="102" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="C5" s="104" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="103" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
+      <c r="G5" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
     </row>
     <row r="6" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="13"/>
-      <c r="C6" s="102" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="C6" s="104" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
+      <c r="G6" s="105" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="105"/>
+      <c r="I6" s="105"/>
     </row>
     <row r="7" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
@@ -6597,20 +6597,20 @@
         <v>2</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F7" s="30"/>
       <c r="G7" s="88" t="s">
         <v>2</v>
       </c>
       <c r="H7" s="88" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I7" s="88" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6715,7 +6715,7 @@
     </row>
     <row r="18" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C18" s="34"/>
       <c r="D18" s="35"/>
@@ -6726,71 +6726,71 @@
       <c r="I18" s="38"/>
     </row>
     <row r="19" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="96" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="96"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="96"/>
-      <c r="G19" s="96"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
+      <c r="B19" s="100" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="100"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="100"/>
     </row>
     <row r="20" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B23" s="97" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="98"/>
-      <c r="D23" s="98"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
+      <c r="B23" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="99"/>
+      <c r="H23" s="99"/>
+      <c r="I23" s="99"/>
     </row>
     <row r="25" spans="2:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="99" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="99"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="99"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="99"/>
+      <c r="B25" s="101" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="101"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="101"/>
+      <c r="H25" s="101"/>
+      <c r="I25" s="101"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="13"/>
-      <c r="C26" s="102" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="102"/>
-      <c r="E26" s="102"/>
+      <c r="C26" s="104" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
       <c r="F26" s="13"/>
-      <c r="G26" s="103" t="s">
-        <v>49</v>
-      </c>
-      <c r="H26" s="103"/>
-      <c r="I26" s="103"/>
+      <c r="G26" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="H26" s="105"/>
+      <c r="I26" s="105"/>
     </row>
     <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="13"/>
-      <c r="C27" s="102" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="102"/>
-      <c r="E27" s="102"/>
+      <c r="C27" s="104" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
       <c r="F27" s="13"/>
-      <c r="G27" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27" s="103"/>
-      <c r="I27" s="103"/>
+      <c r="G27" s="105" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" s="105"/>
+      <c r="I27" s="105"/>
     </row>
     <row r="28" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
@@ -6800,20 +6800,20 @@
         <v>2</v>
       </c>
       <c r="D28" s="77" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E28" s="77" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F28" s="30"/>
       <c r="G28" s="88" t="s">
         <v>2</v>
       </c>
       <c r="H28" s="88" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I28" s="88" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6948,7 +6948,7 @@
     </row>
     <row r="34" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C34" s="23">
         <v>10</v>
@@ -6974,7 +6974,7 @@
     </row>
     <row r="35" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C35" s="23">
         <v>10</v>
@@ -7000,7 +7000,7 @@
     </row>
     <row r="36" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C36" s="23">
         <v>10</v>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="37" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C37" s="23">
         <v>10</v>
@@ -7052,7 +7052,7 @@
     </row>
     <row r="38" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" s="23">
         <v>10</v>
@@ -7078,7 +7078,7 @@
     </row>
     <row r="39" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C39" s="34">
         <v>100</v>
@@ -7103,19 +7103,25 @@
       </c>
     </row>
     <row r="40" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="96" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" s="96"/>
-      <c r="D40" s="96"/>
-      <c r="E40" s="96"/>
-      <c r="F40" s="96"/>
-      <c r="G40" s="96"/>
-      <c r="H40" s="96"/>
-      <c r="I40" s="96"/>
+      <c r="B40" s="100" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="100"/>
+      <c r="D40" s="100"/>
+      <c r="E40" s="100"/>
+      <c r="F40" s="100"/>
+      <c r="G40" s="100"/>
+      <c r="H40" s="100"/>
+      <c r="I40" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="B19:I19"/>
     <mergeCell ref="B25:I25"/>
     <mergeCell ref="B40:I40"/>
@@ -7124,12 +7130,6 @@
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="G27:I27"/>
     <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:I5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7152,56 +7152,56 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B2" s="97" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="98" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
     </row>
     <row r="4" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="99" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
+      <c r="B4" s="101" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="13"/>
-      <c r="C5" s="102" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="C5" s="104" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="103" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
+      <c r="G5" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
     </row>
     <row r="6" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="13"/>
-      <c r="C6" s="102" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="C6" s="104" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
+      <c r="G6" s="105" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="105"/>
+      <c r="I6" s="105"/>
     </row>
     <row r="7" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
@@ -7211,20 +7211,20 @@
         <v>2</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F7" s="30"/>
       <c r="G7" s="88" t="s">
         <v>2</v>
       </c>
       <c r="H7" s="88" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I7" s="88" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7299,7 +7299,7 @@
     </row>
     <row r="15" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C15" s="34"/>
       <c r="D15" s="35"/>
@@ -7310,70 +7310,70 @@
       <c r="I15" s="38"/>
     </row>
     <row r="16" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="96" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
+      <c r="B16" s="100" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="100"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="100"/>
     </row>
     <row r="17" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B19" s="97" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
+      <c r="B19" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="99"/>
     </row>
     <row r="21" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="99" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="99"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="99"/>
-      <c r="H21" s="99"/>
-      <c r="I21" s="99"/>
+      <c r="B21" s="101" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="101"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="101"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B22" s="13"/>
-      <c r="C22" s="102" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="102"/>
-      <c r="E22" s="102"/>
+      <c r="C22" s="104" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="104"/>
+      <c r="E22" s="104"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="103" t="s">
-        <v>49</v>
-      </c>
-      <c r="H22" s="103"/>
-      <c r="I22" s="103"/>
+      <c r="G22" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
     </row>
     <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="13"/>
-      <c r="C23" s="102" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" s="102"/>
-      <c r="E23" s="102"/>
+      <c r="C23" s="104" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
       <c r="F23" s="13"/>
-      <c r="G23" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" s="103"/>
-      <c r="I23" s="103"/>
+      <c r="G23" s="105" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" s="105"/>
+      <c r="I23" s="105"/>
     </row>
     <row r="24" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
@@ -7383,20 +7383,20 @@
         <v>2</v>
       </c>
       <c r="D24" s="77" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E24" s="77" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F24" s="30"/>
       <c r="G24" s="88" t="s">
         <v>2</v>
       </c>
       <c r="H24" s="88" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I24" s="88" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7453,7 +7453,7 @@
     </row>
     <row r="27" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C27" s="23">
         <v>120</v>
@@ -7479,7 +7479,7 @@
     </row>
     <row r="28" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C28" s="23">
         <v>130</v>
@@ -7505,7 +7505,7 @@
     </row>
     <row r="29" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="12" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C29" s="23">
         <v>90</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="30" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C30" s="23">
         <v>110</v>
@@ -7557,7 +7557,7 @@
     </row>
     <row r="31" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="12" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C31" s="23">
         <v>140</v>
@@ -7583,7 +7583,7 @@
     </row>
     <row r="32" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C32" s="34">
         <f>SUM(C25:C31)</f>
@@ -7612,24 +7612,19 @@
       </c>
     </row>
     <row r="33" spans="2:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="96" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="96"/>
-      <c r="G33" s="96"/>
-      <c r="H33" s="96"/>
-      <c r="I33" s="96"/>
+      <c r="B33" s="100" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="100"/>
+      <c r="D33" s="100"/>
+      <c r="E33" s="100"/>
+      <c r="F33" s="100"/>
+      <c r="G33" s="100"/>
+      <c r="H33" s="100"/>
+      <c r="I33" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="B16:I16"/>
     <mergeCell ref="B19:I19"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="C6:E6"/>
@@ -7639,6 +7634,11 @@
     <mergeCell ref="G22:I22"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="G23:I23"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B16:I16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7654,17 +7654,17 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B2" s="52" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B3" s="52" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B5" s="52" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -7687,245 +7687,245 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="B2" s="97" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="Q2" s="97" t="s">
-        <v>102</v>
-      </c>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
-      <c r="T2" s="98"/>
-      <c r="U2" s="98"/>
-      <c r="V2" s="98"/>
-      <c r="W2" s="98"/>
-      <c r="X2" s="98"/>
-      <c r="Y2" s="98"/>
-      <c r="Z2" s="98"/>
-      <c r="AA2" s="98"/>
-      <c r="AB2" s="98"/>
-      <c r="AC2" s="98"/>
-      <c r="AD2" s="98"/>
+      <c r="B2" s="98" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="Q2" s="98" t="s">
+        <v>94</v>
+      </c>
+      <c r="R2" s="99"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="99"/>
+      <c r="U2" s="99"/>
+      <c r="V2" s="99"/>
+      <c r="W2" s="99"/>
+      <c r="X2" s="99"/>
+      <c r="Y2" s="99"/>
+      <c r="Z2" s="99"/>
+      <c r="AA2" s="99"/>
+      <c r="AB2" s="99"/>
+      <c r="AC2" s="99"/>
+      <c r="AD2" s="99"/>
     </row>
     <row r="4" spans="2:30" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="101" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="99"/>
-      <c r="Q4" s="99" t="s">
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="101"/>
+      <c r="Q4" s="101" t="s">
         <v>110</v>
       </c>
-      <c r="R4" s="99"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="99"/>
-      <c r="U4" s="99"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="99"/>
-      <c r="X4" s="99"/>
-      <c r="Y4" s="99"/>
-      <c r="Z4" s="99"/>
-      <c r="AA4" s="99"/>
-      <c r="AB4" s="99"/>
-      <c r="AC4" s="99"/>
-      <c r="AD4" s="99"/>
+      <c r="R4" s="101"/>
+      <c r="S4" s="101"/>
+      <c r="T4" s="101"/>
+      <c r="U4" s="101"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="101"/>
+      <c r="X4" s="101"/>
+      <c r="Y4" s="101"/>
+      <c r="Z4" s="101"/>
+      <c r="AA4" s="101"/>
+      <c r="AB4" s="101"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="101"/>
     </row>
     <row r="5" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="13"/>
       <c r="C5" s="51"/>
-      <c r="D5" s="102" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="102"/>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
+      <c r="D5" s="104" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
       <c r="Q5" s="13"/>
       <c r="R5" s="51"/>
-      <c r="S5" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="T5" s="103"/>
-      <c r="U5" s="103"/>
-      <c r="V5" s="103"/>
-      <c r="W5" s="103"/>
-      <c r="X5" s="103"/>
-      <c r="Y5" s="103"/>
-      <c r="Z5" s="103"/>
-      <c r="AA5" s="103"/>
-      <c r="AB5" s="103"/>
-      <c r="AC5" s="103"/>
-      <c r="AD5" s="103"/>
+      <c r="S5" s="105" t="s">
+        <v>86</v>
+      </c>
+      <c r="T5" s="105"/>
+      <c r="U5" s="105"/>
+      <c r="V5" s="105"/>
+      <c r="W5" s="105"/>
+      <c r="X5" s="105"/>
+      <c r="Y5" s="105"/>
+      <c r="Z5" s="105"/>
+      <c r="AA5" s="105"/>
+      <c r="AB5" s="105"/>
+      <c r="AC5" s="105"/>
+      <c r="AD5" s="105"/>
     </row>
     <row r="6" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="104" t="s">
+      <c r="B6" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="112" t="s">
+      <c r="C6" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="117" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="115"/>
-      <c r="F6" s="114" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="115"/>
-      <c r="H6" s="114" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="115"/>
-      <c r="J6" s="114" t="s">
-        <v>79</v>
-      </c>
-      <c r="K6" s="115"/>
-      <c r="L6" s="114" t="s">
-        <v>61</v>
-      </c>
-      <c r="M6" s="116"/>
-      <c r="N6" s="117" t="s">
-        <v>64</v>
-      </c>
-      <c r="O6" s="116"/>
-      <c r="Q6" s="104" t="s">
+      <c r="D6" s="110" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="111"/>
+      <c r="F6" s="112" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="111"/>
+      <c r="H6" s="112" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="111"/>
+      <c r="J6" s="112" t="s">
+        <v>71</v>
+      </c>
+      <c r="K6" s="111"/>
+      <c r="L6" s="112" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="113"/>
+      <c r="N6" s="110" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" s="113"/>
+      <c r="Q6" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="R6" s="106" t="s">
+      <c r="R6" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="S6" s="108" t="s">
-        <v>85</v>
-      </c>
-      <c r="T6" s="109"/>
-      <c r="U6" s="110" t="s">
-        <v>78</v>
-      </c>
-      <c r="V6" s="109"/>
-      <c r="W6" s="110" t="s">
-        <v>60</v>
-      </c>
-      <c r="X6" s="109"/>
-      <c r="Y6" s="110" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z6" s="109"/>
-      <c r="AA6" s="110" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB6" s="111"/>
-      <c r="AC6" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD6" s="111"/>
+      <c r="S6" s="116" t="s">
+        <v>77</v>
+      </c>
+      <c r="T6" s="117"/>
+      <c r="U6" s="118" t="s">
+        <v>70</v>
+      </c>
+      <c r="V6" s="117"/>
+      <c r="W6" s="118" t="s">
+        <v>54</v>
+      </c>
+      <c r="X6" s="117"/>
+      <c r="Y6" s="118" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z6" s="117"/>
+      <c r="AA6" s="118" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB6" s="119"/>
+      <c r="AC6" s="116" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD6" s="119"/>
     </row>
     <row r="7" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="B7" s="105"/>
-      <c r="C7" s="113"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="109"/>
       <c r="D7" s="81" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E7" s="82" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F7" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G7" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H7" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I7" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J7" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K7" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L7" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="M7" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N7" s="81" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O7" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q7" s="105"/>
-      <c r="R7" s="107"/>
+        <v>57</v>
+      </c>
+      <c r="Q7" s="107"/>
+      <c r="R7" s="115"/>
       <c r="S7" s="94" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T7" s="95" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="U7" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="V7" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="W7" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="X7" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="Y7" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="Z7" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AA7" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AB7" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AC7" s="94" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AD7" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8230,7 +8230,7 @@
     </row>
     <row r="18" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C18" s="50"/>
       <c r="D18" s="47"/>
@@ -8246,7 +8246,7 @@
       <c r="N18" s="44"/>
       <c r="O18" s="38"/>
       <c r="Q18" s="33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R18" s="50"/>
       <c r="S18" s="47"/>
@@ -8263,281 +8263,281 @@
       <c r="AD18" s="38"/>
     </row>
     <row r="19" spans="2:30" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="96" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="96"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="96"/>
-      <c r="G19" s="96"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="96"/>
-      <c r="L19" s="96"/>
-      <c r="M19" s="96"/>
-      <c r="N19" s="96"/>
-      <c r="O19" s="96"/>
-      <c r="Q19" s="96" t="s">
-        <v>72</v>
-      </c>
-      <c r="R19" s="96"/>
-      <c r="S19" s="96"/>
-      <c r="T19" s="96"/>
-      <c r="U19" s="96"/>
-      <c r="V19" s="96"/>
-      <c r="W19" s="96"/>
-      <c r="X19" s="96"/>
-      <c r="Y19" s="96"/>
-      <c r="Z19" s="96"/>
-      <c r="AA19" s="96"/>
-      <c r="AB19" s="96"/>
-      <c r="AC19" s="96"/>
-      <c r="AD19" s="96"/>
+      <c r="B19" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="100"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="100"/>
+      <c r="L19" s="100"/>
+      <c r="M19" s="100"/>
+      <c r="N19" s="100"/>
+      <c r="O19" s="100"/>
+      <c r="Q19" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="R19" s="100"/>
+      <c r="S19" s="100"/>
+      <c r="T19" s="100"/>
+      <c r="U19" s="100"/>
+      <c r="V19" s="100"/>
+      <c r="W19" s="100"/>
+      <c r="X19" s="100"/>
+      <c r="Y19" s="100"/>
+      <c r="Z19" s="100"/>
+      <c r="AA19" s="100"/>
+      <c r="AB19" s="100"/>
+      <c r="AC19" s="100"/>
+      <c r="AD19" s="100"/>
     </row>
     <row r="20" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="B22" s="97" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="98"/>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="98"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="98"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="98"/>
-      <c r="N22" s="98"/>
-      <c r="O22" s="98"/>
-      <c r="Q22" s="97" t="s">
-        <v>104</v>
-      </c>
-      <c r="R22" s="98"/>
-      <c r="S22" s="98"/>
-      <c r="T22" s="98"/>
-      <c r="U22" s="98"/>
-      <c r="V22" s="98"/>
-      <c r="W22" s="98"/>
-      <c r="X22" s="98"/>
-      <c r="Y22" s="98"/>
-      <c r="Z22" s="98"/>
-      <c r="AA22" s="98"/>
-      <c r="AB22" s="98"/>
-      <c r="AC22" s="98"/>
-      <c r="AD22" s="98"/>
+      <c r="B22" s="98" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99"/>
+      <c r="H22" s="99"/>
+      <c r="I22" s="99"/>
+      <c r="J22" s="99"/>
+      <c r="K22" s="99"/>
+      <c r="L22" s="99"/>
+      <c r="M22" s="99"/>
+      <c r="N22" s="99"/>
+      <c r="O22" s="99"/>
+      <c r="Q22" s="98" t="s">
+        <v>96</v>
+      </c>
+      <c r="R22" s="99"/>
+      <c r="S22" s="99"/>
+      <c r="T22" s="99"/>
+      <c r="U22" s="99"/>
+      <c r="V22" s="99"/>
+      <c r="W22" s="99"/>
+      <c r="X22" s="99"/>
+      <c r="Y22" s="99"/>
+      <c r="Z22" s="99"/>
+      <c r="AA22" s="99"/>
+      <c r="AB22" s="99"/>
+      <c r="AC22" s="99"/>
+      <c r="AD22" s="99"/>
     </row>
     <row r="24" spans="2:30" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="99" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="99"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="99"/>
-      <c r="L24" s="99"/>
-      <c r="M24" s="99"/>
-      <c r="N24" s="99"/>
-      <c r="O24" s="99"/>
-      <c r="Q24" s="99" t="s">
+      <c r="B24" s="101" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="101"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="101"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="101"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="101"/>
+      <c r="N24" s="101"/>
+      <c r="O24" s="101"/>
+      <c r="Q24" s="101" t="s">
         <v>111</v>
       </c>
-      <c r="R24" s="99"/>
-      <c r="S24" s="99"/>
-      <c r="T24" s="99"/>
-      <c r="U24" s="99"/>
-      <c r="V24" s="99"/>
-      <c r="W24" s="99"/>
-      <c r="X24" s="99"/>
-      <c r="Y24" s="99"/>
-      <c r="Z24" s="99"/>
-      <c r="AA24" s="99"/>
-      <c r="AB24" s="99"/>
-      <c r="AC24" s="99"/>
-      <c r="AD24" s="99"/>
+      <c r="R24" s="101"/>
+      <c r="S24" s="101"/>
+      <c r="T24" s="101"/>
+      <c r="U24" s="101"/>
+      <c r="V24" s="101"/>
+      <c r="W24" s="101"/>
+      <c r="X24" s="101"/>
+      <c r="Y24" s="101"/>
+      <c r="Z24" s="101"/>
+      <c r="AA24" s="101"/>
+      <c r="AB24" s="101"/>
+      <c r="AC24" s="101"/>
+      <c r="AD24" s="101"/>
     </row>
     <row r="25" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="13"/>
       <c r="C25" s="51"/>
-      <c r="D25" s="102" t="s">
-        <v>94</v>
-      </c>
-      <c r="E25" s="102"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="102"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="102"/>
-      <c r="K25" s="102"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="102"/>
-      <c r="N25" s="102"/>
-      <c r="O25" s="102"/>
+      <c r="D25" s="104" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="104"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="104"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="104"/>
+      <c r="N25" s="104"/>
+      <c r="O25" s="104"/>
       <c r="Q25" s="13"/>
       <c r="R25" s="51"/>
-      <c r="S25" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="T25" s="103"/>
-      <c r="U25" s="103"/>
-      <c r="V25" s="103"/>
-      <c r="W25" s="103"/>
-      <c r="X25" s="103"/>
-      <c r="Y25" s="103"/>
-      <c r="Z25" s="103"/>
-      <c r="AA25" s="103"/>
-      <c r="AB25" s="103"/>
-      <c r="AC25" s="103"/>
-      <c r="AD25" s="103"/>
+      <c r="S25" s="105" t="s">
+        <v>86</v>
+      </c>
+      <c r="T25" s="105"/>
+      <c r="U25" s="105"/>
+      <c r="V25" s="105"/>
+      <c r="W25" s="105"/>
+      <c r="X25" s="105"/>
+      <c r="Y25" s="105"/>
+      <c r="Z25" s="105"/>
+      <c r="AA25" s="105"/>
+      <c r="AB25" s="105"/>
+      <c r="AC25" s="105"/>
+      <c r="AD25" s="105"/>
     </row>
     <row r="26" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="104" t="s">
+      <c r="B26" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="112" t="s">
+      <c r="C26" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="117" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="115"/>
-      <c r="F26" s="114" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" s="115"/>
-      <c r="H26" s="114" t="s">
-        <v>60</v>
-      </c>
-      <c r="I26" s="115"/>
-      <c r="J26" s="114" t="s">
-        <v>79</v>
-      </c>
-      <c r="K26" s="115"/>
-      <c r="L26" s="114" t="s">
-        <v>61</v>
-      </c>
-      <c r="M26" s="116"/>
-      <c r="N26" s="117" t="s">
-        <v>64</v>
-      </c>
-      <c r="O26" s="116"/>
-      <c r="Q26" s="104" t="s">
+      <c r="D26" s="110" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="111"/>
+      <c r="F26" s="112" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="111"/>
+      <c r="H26" s="112" t="s">
+        <v>54</v>
+      </c>
+      <c r="I26" s="111"/>
+      <c r="J26" s="112" t="s">
+        <v>71</v>
+      </c>
+      <c r="K26" s="111"/>
+      <c r="L26" s="112" t="s">
+        <v>55</v>
+      </c>
+      <c r="M26" s="113"/>
+      <c r="N26" s="110" t="s">
+        <v>58</v>
+      </c>
+      <c r="O26" s="113"/>
+      <c r="Q26" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="R26" s="106" t="s">
+      <c r="R26" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="S26" s="108" t="s">
-        <v>85</v>
-      </c>
-      <c r="T26" s="109"/>
-      <c r="U26" s="110" t="s">
-        <v>78</v>
-      </c>
-      <c r="V26" s="109"/>
-      <c r="W26" s="110" t="s">
-        <v>60</v>
-      </c>
-      <c r="X26" s="109"/>
-      <c r="Y26" s="110" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z26" s="109"/>
-      <c r="AA26" s="110" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB26" s="111"/>
-      <c r="AC26" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD26" s="111"/>
+      <c r="S26" s="116" t="s">
+        <v>77</v>
+      </c>
+      <c r="T26" s="117"/>
+      <c r="U26" s="118" t="s">
+        <v>70</v>
+      </c>
+      <c r="V26" s="117"/>
+      <c r="W26" s="118" t="s">
+        <v>54</v>
+      </c>
+      <c r="X26" s="117"/>
+      <c r="Y26" s="118" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z26" s="117"/>
+      <c r="AA26" s="118" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB26" s="119"/>
+      <c r="AC26" s="116" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD26" s="119"/>
     </row>
     <row r="27" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="B27" s="105"/>
-      <c r="C27" s="113"/>
+      <c r="B27" s="107"/>
+      <c r="C27" s="109"/>
       <c r="D27" s="81" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E27" s="82" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F27" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G27" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H27" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I27" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J27" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K27" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L27" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="M27" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N27" s="81" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O27" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q27" s="105"/>
-      <c r="R27" s="107"/>
+        <v>57</v>
+      </c>
+      <c r="Q27" s="107"/>
+      <c r="R27" s="115"/>
       <c r="S27" s="94" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T27" s="95" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="U27" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="V27" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="W27" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="X27" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="Y27" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="Z27" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AA27" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AB27" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AC27" s="94" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AD27" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -9042,7 +9042,7 @@
     </row>
     <row r="33" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C33" s="19">
         <v>10</v>
@@ -9091,7 +9091,7 @@
         <v>0.1</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R33" s="19">
         <v>20</v>
@@ -9142,7 +9142,7 @@
     </row>
     <row r="34" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C34" s="19">
         <v>10</v>
@@ -9191,7 +9191,7 @@
         <v>0.1</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R34" s="19">
         <v>20</v>
@@ -9242,7 +9242,7 @@
     </row>
     <row r="35" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C35" s="19">
         <v>10</v>
@@ -9291,7 +9291,7 @@
         <v>0</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R35" s="19">
         <v>20</v>
@@ -9342,7 +9342,7 @@
     </row>
     <row r="36" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C36" s="19">
         <v>10</v>
@@ -9391,7 +9391,7 @@
         <v>0.3</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R36" s="19">
         <v>20</v>
@@ -9442,7 +9442,7 @@
     </row>
     <row r="37" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" s="19">
         <v>10</v>
@@ -9491,7 +9491,7 @@
         <v>0.1</v>
       </c>
       <c r="Q37" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R37" s="19">
         <v>20</v>
@@ -9542,7 +9542,7 @@
     </row>
     <row r="38" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C38" s="50">
         <f>SUM(C28:C37)</f>
@@ -9597,7 +9597,7 @@
         <v>0.1</v>
       </c>
       <c r="Q38" s="33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R38" s="50">
         <f>SUM(R28:R37)</f>
@@ -9653,49 +9653,65 @@
       </c>
     </row>
     <row r="39" spans="2:30" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="96" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" s="96"/>
-      <c r="D39" s="96"/>
-      <c r="E39" s="96"/>
-      <c r="F39" s="96"/>
-      <c r="G39" s="96"/>
-      <c r="H39" s="96"/>
-      <c r="I39" s="96"/>
-      <c r="J39" s="96"/>
-      <c r="K39" s="96"/>
-      <c r="L39" s="96"/>
-      <c r="M39" s="96"/>
-      <c r="N39" s="96"/>
-      <c r="O39" s="96"/>
-      <c r="Q39" s="96" t="s">
-        <v>72</v>
-      </c>
-      <c r="R39" s="96"/>
-      <c r="S39" s="96"/>
-      <c r="T39" s="96"/>
-      <c r="U39" s="96"/>
-      <c r="V39" s="96"/>
-      <c r="W39" s="96"/>
-      <c r="X39" s="96"/>
-      <c r="Y39" s="96"/>
-      <c r="Z39" s="96"/>
-      <c r="AA39" s="96"/>
-      <c r="AB39" s="96"/>
-      <c r="AC39" s="96"/>
-      <c r="AD39" s="96"/>
+      <c r="B39" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="100"/>
+      <c r="D39" s="100"/>
+      <c r="E39" s="100"/>
+      <c r="F39" s="100"/>
+      <c r="G39" s="100"/>
+      <c r="H39" s="100"/>
+      <c r="I39" s="100"/>
+      <c r="J39" s="100"/>
+      <c r="K39" s="100"/>
+      <c r="L39" s="100"/>
+      <c r="M39" s="100"/>
+      <c r="N39" s="100"/>
+      <c r="O39" s="100"/>
+      <c r="Q39" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="R39" s="100"/>
+      <c r="S39" s="100"/>
+      <c r="T39" s="100"/>
+      <c r="U39" s="100"/>
+      <c r="V39" s="100"/>
+      <c r="W39" s="100"/>
+      <c r="X39" s="100"/>
+      <c r="Y39" s="100"/>
+      <c r="Z39" s="100"/>
+      <c r="AA39" s="100"/>
+      <c r="AB39" s="100"/>
+      <c r="AC39" s="100"/>
+      <c r="AD39" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B39:O39"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="Q39:AD39"/>
+    <mergeCell ref="Q19:AD19"/>
+    <mergeCell ref="Q22:AD22"/>
+    <mergeCell ref="Q24:AD24"/>
+    <mergeCell ref="S25:AD25"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="R26:R27"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="Y26:Z26"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="AC26:AD26"/>
+    <mergeCell ref="Q2:AD2"/>
+    <mergeCell ref="Q4:AD4"/>
+    <mergeCell ref="S5:AD5"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="AC6:AD6"/>
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="B4:O4"/>
     <mergeCell ref="C6:C7"/>
@@ -9712,30 +9728,14 @@
     <mergeCell ref="D5:O5"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="Q2:AD2"/>
-    <mergeCell ref="Q4:AD4"/>
-    <mergeCell ref="S5:AD5"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="AC6:AD6"/>
-    <mergeCell ref="Q39:AD39"/>
-    <mergeCell ref="Q19:AD19"/>
-    <mergeCell ref="Q22:AD22"/>
-    <mergeCell ref="Q24:AD24"/>
-    <mergeCell ref="S25:AD25"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="R26:R27"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="W26:X26"/>
-    <mergeCell ref="Y26:Z26"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="AC26:AD26"/>
+    <mergeCell ref="B39:O39"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -9759,245 +9759,245 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="B2" s="97" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="Q2" s="97" t="s">
-        <v>102</v>
-      </c>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
-      <c r="T2" s="98"/>
-      <c r="U2" s="98"/>
-      <c r="V2" s="98"/>
-      <c r="W2" s="98"/>
-      <c r="X2" s="98"/>
-      <c r="Y2" s="98"/>
-      <c r="Z2" s="98"/>
-      <c r="AA2" s="98"/>
-      <c r="AB2" s="98"/>
-      <c r="AC2" s="98"/>
-      <c r="AD2" s="98"/>
+      <c r="B2" s="98" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="Q2" s="98" t="s">
+        <v>94</v>
+      </c>
+      <c r="R2" s="99"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="99"/>
+      <c r="U2" s="99"/>
+      <c r="V2" s="99"/>
+      <c r="W2" s="99"/>
+      <c r="X2" s="99"/>
+      <c r="Y2" s="99"/>
+      <c r="Z2" s="99"/>
+      <c r="AA2" s="99"/>
+      <c r="AB2" s="99"/>
+      <c r="AC2" s="99"/>
+      <c r="AD2" s="99"/>
     </row>
     <row r="4" spans="2:30" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="99" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="99"/>
-      <c r="Q4" s="99" t="s">
-        <v>114</v>
-      </c>
-      <c r="R4" s="99"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="99"/>
-      <c r="U4" s="99"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="99"/>
-      <c r="X4" s="99"/>
-      <c r="Y4" s="99"/>
-      <c r="Z4" s="99"/>
-      <c r="AA4" s="99"/>
-      <c r="AB4" s="99"/>
-      <c r="AC4" s="99"/>
-      <c r="AD4" s="99"/>
+      <c r="B4" s="101" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="101"/>
+      <c r="Q4" s="101" t="s">
+        <v>116</v>
+      </c>
+      <c r="R4" s="101"/>
+      <c r="S4" s="101"/>
+      <c r="T4" s="101"/>
+      <c r="U4" s="101"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="101"/>
+      <c r="X4" s="101"/>
+      <c r="Y4" s="101"/>
+      <c r="Z4" s="101"/>
+      <c r="AA4" s="101"/>
+      <c r="AB4" s="101"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="101"/>
     </row>
     <row r="5" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="13"/>
       <c r="C5" s="51"/>
-      <c r="D5" s="102" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="102"/>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
+      <c r="D5" s="104" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
       <c r="Q5" s="13"/>
       <c r="R5" s="51"/>
-      <c r="S5" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="T5" s="103"/>
-      <c r="U5" s="103"/>
-      <c r="V5" s="103"/>
-      <c r="W5" s="103"/>
-      <c r="X5" s="103"/>
-      <c r="Y5" s="103"/>
-      <c r="Z5" s="103"/>
-      <c r="AA5" s="103"/>
-      <c r="AB5" s="103"/>
-      <c r="AC5" s="103"/>
-      <c r="AD5" s="103"/>
+      <c r="S5" s="105" t="s">
+        <v>86</v>
+      </c>
+      <c r="T5" s="105"/>
+      <c r="U5" s="105"/>
+      <c r="V5" s="105"/>
+      <c r="W5" s="105"/>
+      <c r="X5" s="105"/>
+      <c r="Y5" s="105"/>
+      <c r="Z5" s="105"/>
+      <c r="AA5" s="105"/>
+      <c r="AB5" s="105"/>
+      <c r="AC5" s="105"/>
+      <c r="AD5" s="105"/>
     </row>
     <row r="6" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="112" t="s">
+      <c r="B6" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="117" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="115"/>
-      <c r="F6" s="114" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="115"/>
-      <c r="H6" s="114" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="115"/>
-      <c r="J6" s="114" t="s">
-        <v>79</v>
-      </c>
-      <c r="K6" s="115"/>
-      <c r="L6" s="114" t="s">
-        <v>61</v>
-      </c>
-      <c r="M6" s="116"/>
-      <c r="N6" s="117" t="s">
-        <v>64</v>
-      </c>
-      <c r="O6" s="116"/>
-      <c r="Q6" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="R6" s="106" t="s">
+      <c r="D6" s="110" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="111"/>
+      <c r="F6" s="112" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="111"/>
+      <c r="H6" s="112" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="111"/>
+      <c r="J6" s="112" t="s">
+        <v>71</v>
+      </c>
+      <c r="K6" s="111"/>
+      <c r="L6" s="112" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="113"/>
+      <c r="N6" s="110" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" s="113"/>
+      <c r="Q6" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="R6" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="S6" s="108" t="s">
-        <v>85</v>
-      </c>
-      <c r="T6" s="109"/>
-      <c r="U6" s="110" t="s">
-        <v>78</v>
-      </c>
-      <c r="V6" s="109"/>
-      <c r="W6" s="110" t="s">
-        <v>60</v>
-      </c>
-      <c r="X6" s="109"/>
-      <c r="Y6" s="110" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z6" s="109"/>
-      <c r="AA6" s="110" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB6" s="111"/>
-      <c r="AC6" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD6" s="111"/>
+      <c r="S6" s="116" t="s">
+        <v>77</v>
+      </c>
+      <c r="T6" s="117"/>
+      <c r="U6" s="118" t="s">
+        <v>70</v>
+      </c>
+      <c r="V6" s="117"/>
+      <c r="W6" s="118" t="s">
+        <v>54</v>
+      </c>
+      <c r="X6" s="117"/>
+      <c r="Y6" s="118" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z6" s="117"/>
+      <c r="AA6" s="118" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB6" s="119"/>
+      <c r="AC6" s="116" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD6" s="119"/>
     </row>
     <row r="7" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="B7" s="105"/>
-      <c r="C7" s="113"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="109"/>
       <c r="D7" s="81" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E7" s="82" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F7" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G7" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H7" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I7" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J7" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K7" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L7" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="M7" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N7" s="81" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O7" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q7" s="105"/>
-      <c r="R7" s="107"/>
+        <v>57</v>
+      </c>
+      <c r="Q7" s="107"/>
+      <c r="R7" s="115"/>
       <c r="S7" s="94" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T7" s="95" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="U7" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="V7" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="W7" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="X7" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="Y7" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="Z7" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AA7" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AB7" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AC7" s="94" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AD7" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -10302,7 +10302,7 @@
     </row>
     <row r="18" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C18" s="50"/>
       <c r="D18" s="47"/>
@@ -10318,7 +10318,7 @@
       <c r="N18" s="44"/>
       <c r="O18" s="38"/>
       <c r="Q18" s="33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R18" s="50"/>
       <c r="S18" s="47"/>
@@ -10335,10 +10335,10 @@
       <c r="AD18" s="38"/>
     </row>
     <row r="19" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="119"/>
+      <c r="B19" s="120" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="121"/>
       <c r="D19" s="89"/>
       <c r="E19" s="90"/>
       <c r="F19" s="91"/>
@@ -10351,10 +10351,10 @@
       <c r="M19" s="90"/>
       <c r="N19" s="89"/>
       <c r="O19" s="92"/>
-      <c r="Q19" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="R19" s="119"/>
+      <c r="Q19" s="120" t="s">
+        <v>89</v>
+      </c>
+      <c r="R19" s="121"/>
       <c r="S19" s="89"/>
       <c r="T19" s="90"/>
       <c r="U19" s="91"/>
@@ -10369,281 +10369,281 @@
       <c r="AD19" s="92"/>
     </row>
     <row r="20" spans="2:30" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="96" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="96"/>
-      <c r="K20" s="96"/>
-      <c r="L20" s="96"/>
-      <c r="M20" s="96"/>
-      <c r="N20" s="96"/>
-      <c r="O20" s="96"/>
-      <c r="Q20" s="96" t="s">
-        <v>72</v>
-      </c>
-      <c r="R20" s="96"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="96"/>
-      <c r="U20" s="96"/>
-      <c r="V20" s="96"/>
-      <c r="W20" s="96"/>
-      <c r="X20" s="96"/>
-      <c r="Y20" s="96"/>
-      <c r="Z20" s="96"/>
-      <c r="AA20" s="96"/>
-      <c r="AB20" s="96"/>
-      <c r="AC20" s="96"/>
-      <c r="AD20" s="96"/>
+      <c r="B20" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="100"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="100"/>
+      <c r="N20" s="100"/>
+      <c r="O20" s="100"/>
+      <c r="Q20" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="R20" s="100"/>
+      <c r="S20" s="100"/>
+      <c r="T20" s="100"/>
+      <c r="U20" s="100"/>
+      <c r="V20" s="100"/>
+      <c r="W20" s="100"/>
+      <c r="X20" s="100"/>
+      <c r="Y20" s="100"/>
+      <c r="Z20" s="100"/>
+      <c r="AA20" s="100"/>
+      <c r="AB20" s="100"/>
+      <c r="AC20" s="100"/>
+      <c r="AD20" s="100"/>
     </row>
     <row r="21" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="B23" s="97" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" s="98"/>
-      <c r="D23" s="98"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
-      <c r="J23" s="98"/>
-      <c r="K23" s="98"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="98"/>
-      <c r="N23" s="98"/>
-      <c r="O23" s="98"/>
-      <c r="Q23" s="97" t="s">
-        <v>104</v>
-      </c>
-      <c r="R23" s="98"/>
-      <c r="S23" s="98"/>
-      <c r="T23" s="98"/>
-      <c r="U23" s="98"/>
-      <c r="V23" s="98"/>
-      <c r="W23" s="98"/>
-      <c r="X23" s="98"/>
-      <c r="Y23" s="98"/>
-      <c r="Z23" s="98"/>
-      <c r="AA23" s="98"/>
-      <c r="AB23" s="98"/>
-      <c r="AC23" s="98"/>
-      <c r="AD23" s="98"/>
+      <c r="B23" s="98" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="99"/>
+      <c r="H23" s="99"/>
+      <c r="I23" s="99"/>
+      <c r="J23" s="99"/>
+      <c r="K23" s="99"/>
+      <c r="L23" s="99"/>
+      <c r="M23" s="99"/>
+      <c r="N23" s="99"/>
+      <c r="O23" s="99"/>
+      <c r="Q23" s="98" t="s">
+        <v>96</v>
+      </c>
+      <c r="R23" s="99"/>
+      <c r="S23" s="99"/>
+      <c r="T23" s="99"/>
+      <c r="U23" s="99"/>
+      <c r="V23" s="99"/>
+      <c r="W23" s="99"/>
+      <c r="X23" s="99"/>
+      <c r="Y23" s="99"/>
+      <c r="Z23" s="99"/>
+      <c r="AA23" s="99"/>
+      <c r="AB23" s="99"/>
+      <c r="AC23" s="99"/>
+      <c r="AD23" s="99"/>
     </row>
     <row r="25" spans="2:30" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="99" t="s">
-        <v>113</v>
-      </c>
-      <c r="C25" s="99"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="99"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="99"/>
-      <c r="J25" s="99"/>
-      <c r="K25" s="99"/>
-      <c r="L25" s="99"/>
-      <c r="M25" s="99"/>
-      <c r="N25" s="99"/>
-      <c r="O25" s="99"/>
-      <c r="Q25" s="99" t="s">
+      <c r="B25" s="101" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="101"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="101"/>
+      <c r="H25" s="101"/>
+      <c r="I25" s="101"/>
+      <c r="J25" s="101"/>
+      <c r="K25" s="101"/>
+      <c r="L25" s="101"/>
+      <c r="M25" s="101"/>
+      <c r="N25" s="101"/>
+      <c r="O25" s="101"/>
+      <c r="Q25" s="101" t="s">
         <v>115</v>
       </c>
-      <c r="R25" s="99"/>
-      <c r="S25" s="99"/>
-      <c r="T25" s="99"/>
-      <c r="U25" s="99"/>
-      <c r="V25" s="99"/>
-      <c r="W25" s="99"/>
-      <c r="X25" s="99"/>
-      <c r="Y25" s="99"/>
-      <c r="Z25" s="99"/>
-      <c r="AA25" s="99"/>
-      <c r="AB25" s="99"/>
-      <c r="AC25" s="99"/>
-      <c r="AD25" s="99"/>
+      <c r="R25" s="101"/>
+      <c r="S25" s="101"/>
+      <c r="T25" s="101"/>
+      <c r="U25" s="101"/>
+      <c r="V25" s="101"/>
+      <c r="W25" s="101"/>
+      <c r="X25" s="101"/>
+      <c r="Y25" s="101"/>
+      <c r="Z25" s="101"/>
+      <c r="AA25" s="101"/>
+      <c r="AB25" s="101"/>
+      <c r="AC25" s="101"/>
+      <c r="AD25" s="101"/>
     </row>
     <row r="26" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="13"/>
       <c r="C26" s="51"/>
-      <c r="D26" s="102" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" s="102"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="102"/>
-      <c r="H26" s="102"/>
-      <c r="I26" s="102"/>
-      <c r="J26" s="102"/>
-      <c r="K26" s="102"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="102"/>
-      <c r="N26" s="102"/>
-      <c r="O26" s="102"/>
+      <c r="D26" s="104" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="104"/>
+      <c r="F26" s="104"/>
+      <c r="G26" s="104"/>
+      <c r="H26" s="104"/>
+      <c r="I26" s="104"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="104"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="104"/>
+      <c r="N26" s="104"/>
+      <c r="O26" s="104"/>
       <c r="Q26" s="13"/>
       <c r="R26" s="51"/>
-      <c r="S26" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="T26" s="103"/>
-      <c r="U26" s="103"/>
-      <c r="V26" s="103"/>
-      <c r="W26" s="103"/>
-      <c r="X26" s="103"/>
-      <c r="Y26" s="103"/>
-      <c r="Z26" s="103"/>
-      <c r="AA26" s="103"/>
-      <c r="AB26" s="103"/>
-      <c r="AC26" s="103"/>
-      <c r="AD26" s="103"/>
+      <c r="S26" s="105" t="s">
+        <v>86</v>
+      </c>
+      <c r="T26" s="105"/>
+      <c r="U26" s="105"/>
+      <c r="V26" s="105"/>
+      <c r="W26" s="105"/>
+      <c r="X26" s="105"/>
+      <c r="Y26" s="105"/>
+      <c r="Z26" s="105"/>
+      <c r="AA26" s="105"/>
+      <c r="AB26" s="105"/>
+      <c r="AC26" s="105"/>
+      <c r="AD26" s="105"/>
     </row>
     <row r="27" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="112" t="s">
+      <c r="B27" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="117" t="s">
-        <v>85</v>
-      </c>
-      <c r="E27" s="115"/>
-      <c r="F27" s="114" t="s">
-        <v>78</v>
-      </c>
-      <c r="G27" s="115"/>
-      <c r="H27" s="114" t="s">
-        <v>60</v>
-      </c>
-      <c r="I27" s="115"/>
-      <c r="J27" s="114" t="s">
-        <v>79</v>
-      </c>
-      <c r="K27" s="115"/>
-      <c r="L27" s="114" t="s">
-        <v>61</v>
-      </c>
-      <c r="M27" s="116"/>
-      <c r="N27" s="117" t="s">
-        <v>64</v>
-      </c>
-      <c r="O27" s="116"/>
-      <c r="Q27" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="R27" s="106" t="s">
+      <c r="D27" s="110" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="111"/>
+      <c r="F27" s="112" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="111"/>
+      <c r="H27" s="112" t="s">
+        <v>54</v>
+      </c>
+      <c r="I27" s="111"/>
+      <c r="J27" s="112" t="s">
+        <v>71</v>
+      </c>
+      <c r="K27" s="111"/>
+      <c r="L27" s="112" t="s">
+        <v>55</v>
+      </c>
+      <c r="M27" s="113"/>
+      <c r="N27" s="110" t="s">
+        <v>58</v>
+      </c>
+      <c r="O27" s="113"/>
+      <c r="Q27" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="R27" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="S27" s="108" t="s">
-        <v>85</v>
-      </c>
-      <c r="T27" s="109"/>
-      <c r="U27" s="110" t="s">
-        <v>78</v>
-      </c>
-      <c r="V27" s="109"/>
-      <c r="W27" s="110" t="s">
-        <v>60</v>
-      </c>
-      <c r="X27" s="109"/>
-      <c r="Y27" s="110" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z27" s="109"/>
-      <c r="AA27" s="110" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB27" s="111"/>
-      <c r="AC27" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD27" s="111"/>
+      <c r="S27" s="116" t="s">
+        <v>77</v>
+      </c>
+      <c r="T27" s="117"/>
+      <c r="U27" s="118" t="s">
+        <v>70</v>
+      </c>
+      <c r="V27" s="117"/>
+      <c r="W27" s="118" t="s">
+        <v>54</v>
+      </c>
+      <c r="X27" s="117"/>
+      <c r="Y27" s="118" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z27" s="117"/>
+      <c r="AA27" s="118" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB27" s="119"/>
+      <c r="AC27" s="116" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD27" s="119"/>
     </row>
     <row r="28" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="B28" s="105"/>
-      <c r="C28" s="113"/>
+      <c r="B28" s="107"/>
+      <c r="C28" s="109"/>
       <c r="D28" s="81" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E28" s="82" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F28" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G28" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H28" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I28" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J28" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K28" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L28" s="77" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="M28" s="77" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N28" s="81" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O28" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q28" s="105"/>
-      <c r="R28" s="107"/>
+        <v>57</v>
+      </c>
+      <c r="Q28" s="107"/>
+      <c r="R28" s="115"/>
       <c r="S28" s="94" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T28" s="95" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="U28" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="V28" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="W28" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="X28" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="Y28" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="Z28" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AA28" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AB28" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AC28" s="94" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AD28" s="88" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -10848,7 +10848,7 @@
     </row>
     <row r="31" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C31" s="19">
         <v>120</v>
@@ -10897,7 +10897,7 @@
         <v>8.3333333333333332E-3</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="R31" s="19">
         <v>240</v>
@@ -10948,7 +10948,7 @@
     </row>
     <row r="32" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C32" s="19">
         <v>130</v>
@@ -10997,7 +10997,7 @@
         <v>1.5384615384615385E-2</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="R32" s="19">
         <v>260</v>
@@ -11048,7 +11048,7 @@
     </row>
     <row r="33" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="12" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C33" s="19">
         <v>90</v>
@@ -11097,7 +11097,7 @@
         <v>7.7777777777777779E-2</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="R33" s="19">
         <v>180</v>
@@ -11148,7 +11148,7 @@
     </row>
     <row r="34" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C34" s="19">
         <v>110</v>
@@ -11197,7 +11197,7 @@
         <v>6.363636363636363E-2</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="R34" s="19">
         <v>220</v>
@@ -11248,7 +11248,7 @@
     </row>
     <row r="35" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="12" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C35" s="19">
         <v>140</v>
@@ -11297,7 +11297,7 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="R35" s="19">
         <v>280</v>
@@ -11348,7 +11348,7 @@
     </row>
     <row r="36" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C36" s="50">
         <f>SUM(C29:C35)</f>
@@ -11403,7 +11403,7 @@
         <v>4.5783132530120479E-2</v>
       </c>
       <c r="Q36" s="33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R36" s="50">
         <f>SUM(R29:R35)</f>
@@ -11459,10 +11459,10 @@
       </c>
     </row>
     <row r="37" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" s="119"/>
+      <c r="B37" s="120" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="121"/>
       <c r="D37" s="89"/>
       <c r="E37" s="90">
         <f>D36/$N$36</f>
@@ -11490,10 +11490,10 @@
       </c>
       <c r="N37" s="89"/>
       <c r="O37" s="92"/>
-      <c r="Q37" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="R37" s="119"/>
+      <c r="Q37" s="120" t="s">
+        <v>89</v>
+      </c>
+      <c r="R37" s="121"/>
       <c r="S37" s="89"/>
       <c r="T37" s="90">
         <f>S36/$AC$36</f>
@@ -11523,49 +11523,69 @@
       <c r="AD37" s="92"/>
     </row>
     <row r="38" spans="2:30" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="96" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="96"/>
-      <c r="D38" s="96"/>
-      <c r="E38" s="96"/>
-      <c r="F38" s="96"/>
-      <c r="G38" s="96"/>
-      <c r="H38" s="96"/>
-      <c r="I38" s="96"/>
-      <c r="J38" s="96"/>
-      <c r="K38" s="96"/>
-      <c r="L38" s="96"/>
-      <c r="M38" s="96"/>
-      <c r="N38" s="96"/>
-      <c r="O38" s="96"/>
-      <c r="Q38" s="96" t="s">
-        <v>72</v>
-      </c>
-      <c r="R38" s="96"/>
-      <c r="S38" s="96"/>
-      <c r="T38" s="96"/>
-      <c r="U38" s="96"/>
-      <c r="V38" s="96"/>
-      <c r="W38" s="96"/>
-      <c r="X38" s="96"/>
-      <c r="Y38" s="96"/>
-      <c r="Z38" s="96"/>
-      <c r="AA38" s="96"/>
-      <c r="AB38" s="96"/>
-      <c r="AC38" s="96"/>
-      <c r="AD38" s="96"/>
+      <c r="B38" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" s="100"/>
+      <c r="D38" s="100"/>
+      <c r="E38" s="100"/>
+      <c r="F38" s="100"/>
+      <c r="G38" s="100"/>
+      <c r="H38" s="100"/>
+      <c r="I38" s="100"/>
+      <c r="J38" s="100"/>
+      <c r="K38" s="100"/>
+      <c r="L38" s="100"/>
+      <c r="M38" s="100"/>
+      <c r="N38" s="100"/>
+      <c r="O38" s="100"/>
+      <c r="Q38" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="R38" s="100"/>
+      <c r="S38" s="100"/>
+      <c r="T38" s="100"/>
+      <c r="U38" s="100"/>
+      <c r="V38" s="100"/>
+      <c r="W38" s="100"/>
+      <c r="X38" s="100"/>
+      <c r="Y38" s="100"/>
+      <c r="Z38" s="100"/>
+      <c r="AA38" s="100"/>
+      <c r="AB38" s="100"/>
+      <c r="AC38" s="100"/>
+      <c r="AD38" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="Q38:AD38"/>
+    <mergeCell ref="Q25:AD25"/>
+    <mergeCell ref="S26:AD26"/>
+    <mergeCell ref="Q27:Q28"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="W27:X27"/>
+    <mergeCell ref="Y27:Z27"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="AC27:AD27"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="Q2:AD2"/>
+    <mergeCell ref="Q4:AD4"/>
+    <mergeCell ref="S5:AD5"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="AC6:AD6"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:AD20"/>
+    <mergeCell ref="Q23:AD23"/>
     <mergeCell ref="H27:I27"/>
     <mergeCell ref="B38:O38"/>
     <mergeCell ref="D5:O5"/>
@@ -11582,34 +11602,14 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="L6:M6"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="Q2:AD2"/>
-    <mergeCell ref="Q4:AD4"/>
-    <mergeCell ref="S5:AD5"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="AC6:AD6"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:AD20"/>
-    <mergeCell ref="Q23:AD23"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="Q38:AD38"/>
-    <mergeCell ref="Q25:AD25"/>
-    <mergeCell ref="S26:AD26"/>
-    <mergeCell ref="Q27:Q28"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="W27:X27"/>
-    <mergeCell ref="Y27:Z27"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="AC27:AD27"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -11631,86 +11631,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B2" s="97" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="98" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="99" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
+      <c r="B4" s="101" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
     </row>
     <row r="5" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="104" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="112" t="s">
+      <c r="B5" s="106" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="108" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="124" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E5" s="125"/>
-      <c r="F5" s="122" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="123"/>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
+      <c r="F5" s="128" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="129"/>
+      <c r="H5" s="129"/>
+      <c r="I5" s="129"/>
     </row>
     <row r="6" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="120"/>
-      <c r="C6" s="121"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="123"/>
       <c r="D6" s="126"/>
       <c r="E6" s="127"/>
-      <c r="F6" s="114" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="115"/>
-      <c r="H6" s="114" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="116"/>
+      <c r="F6" s="112" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="111"/>
+      <c r="H6" s="112" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="113"/>
     </row>
     <row r="7" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="105"/>
-      <c r="C7" s="113"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="109"/>
       <c r="D7" s="79" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E7" s="80" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F7" s="80" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G7" s="78" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H7" s="80" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I7" s="78" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="53" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="54"/>
@@ -11721,26 +11721,26 @@
       <c r="I8" s="56"/>
     </row>
     <row r="9" spans="2:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="96" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
+      <c r="B9" s="100" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="100"/>
     </row>
     <row r="10" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="101"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="100"/>
-      <c r="H10" s="100"/>
-      <c r="I10" s="100"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="103"/>
+      <c r="I10" s="103"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B11" s="40"/>
@@ -11763,87 +11763,87 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="97" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="98"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
+      <c r="B13" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
     </row>
     <row r="14" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="99" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="99"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="99"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="99"/>
+      <c r="B15" s="101" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="101"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="101"/>
+      <c r="I15" s="101"/>
     </row>
     <row r="16" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="104" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="112" t="s">
+      <c r="B16" s="106" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="108" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="124" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E16" s="125"/>
-      <c r="F16" s="122" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="123"/>
-      <c r="H16" s="123"/>
-      <c r="I16" s="123"/>
+      <c r="F16" s="128" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="129"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="129"/>
     </row>
     <row r="17" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="120"/>
-      <c r="C17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="123"/>
       <c r="D17" s="126"/>
       <c r="E17" s="127"/>
-      <c r="F17" s="114" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="115"/>
-      <c r="H17" s="114" t="s">
-        <v>69</v>
-      </c>
-      <c r="I17" s="116"/>
+      <c r="F17" s="112" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="111"/>
+      <c r="H17" s="112" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" s="113"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B18" s="105"/>
-      <c r="C18" s="113"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="109"/>
       <c r="D18" s="79" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E18" s="80" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F18" s="80" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G18" s="78" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H18" s="80" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I18" s="78" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="53" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C19" s="20">
         <v>2400</v>
@@ -11871,16 +11871,16 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="96" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
+      <c r="B20" s="100" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="100"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="100"/>
     </row>
     <row r="21" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -11889,14 +11889,6 @@
     <row r="26" spans="2:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B15:I15"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:E17"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:I17"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="B13:I13"/>
@@ -11908,12 +11900,47 @@
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="D5:E6"/>
     <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:E17"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:I17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f53cdae7-58e9-463a-80c4-ff1f1a52caeb" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7a2ce8f2-2204-4367-a41c-b735e7c03037">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Person xmlns="7a2ce8f2-2204-4367-a41c-b735e7c03037">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Person>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BF11AF2F54683D48B47D51E7C5C20D0A" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6c3ec6b3112fff6afcb2e1bceac7318f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7a2ce8f2-2204-4367-a41c-b735e7c03037" xmlns:ns3="f53cdae7-58e9-463a-80c4-ff1f1a52caeb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1733b412cddd9f821d661af390973bad" ns2:_="" ns3:_="">
     <xsd:import namespace="7a2ce8f2-2204-4367-a41c-b735e7c03037"/>
@@ -12188,34 +12215,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f53cdae7-58e9-463a-80c4-ff1f1a52caeb" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7a2ce8f2-2204-4367-a41c-b735e7c03037">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Person xmlns="7a2ce8f2-2204-4367-a41c-b735e7c03037">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Person>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B3296EB-6EE8-4120-9EBF-72BCE60350D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CF37811-5B39-40AB-A48E-E8D821EC7E51}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f53cdae7-58e9-463a-80c4-ff1f1a52caeb"/>
+    <ds:schemaRef ds:uri="7a2ce8f2-2204-4367-a41c-b735e7c03037"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C671297C-EBCA-4879-B8AC-4D3F309E1D7D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12232,23 +12251,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CF37811-5B39-40AB-A48E-E8D821EC7E51}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f53cdae7-58e9-463a-80c4-ff1f1a52caeb"/>
-    <ds:schemaRef ds:uri="7a2ce8f2-2204-4367-a41c-b735e7c03037"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B3296EB-6EE8-4120-9EBF-72BCE60350D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>